--- a/Reports/Device/Register_averaging/Register_averaging.xlsx
+++ b/Reports/Device/Register_averaging/Register_averaging.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20827"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OpenServer\domains\REPORTS-test\Reports\Device\Register_averaging\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB8D7E2-F265-4DBC-80BF-A3610DC7E77B}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="60" windowWidth="17100" windowHeight="10110"/>
+    <workbookView xWindow="360" yWindow="60" windowWidth="17100" windowHeight="10110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -81,9 +87,6 @@
     <t>Зав.Номер</t>
   </si>
   <si>
-    <t>Марта</t>
-  </si>
-  <si>
     <t>$t1['mark']</t>
   </si>
   <si>
@@ -102,9 +105,6 @@
     <t>Дата ввода в эксплуатацию</t>
   </si>
   <si>
-    <t>Скрок экспл. (лет)</t>
-  </si>
-  <si>
     <t>$t1['name_type_accrual']</t>
   </si>
   <si>
@@ -136,17 +136,23 @@
   </si>
   <si>
     <t>$DATE_t1['dala_start']</t>
+  </si>
+  <si>
+    <t>Марка</t>
+  </si>
+  <si>
+    <t>Срок экспл. (лет)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;₽&quot;;[Red]\-#,##0.00\ &quot;₽&quot;"/>
     <numFmt numFmtId="164" formatCode="#,##0.000_ ;[Red]\-#,##0.000\ "/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial Cyr"/>
@@ -292,13 +298,21 @@
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 3" xfId="1"/>
-    <cellStyle name="Обычный 4" xfId="2"/>
-    <cellStyle name="Обычный 5" xfId="3"/>
-    <cellStyle name="Обычный 6" xfId="4"/>
+    <cellStyle name="Обычный 3" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Обычный 4" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Обычный 5" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Обычный 6" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -345,7 +359,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -377,9 +391,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -411,6 +443,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Стандартная">
@@ -586,12 +636,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Y5"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.5703125" style="1" customWidth="1"/>
     <col min="2" max="2" width="14.28515625" style="1" customWidth="1"/>
@@ -605,9 +655,9 @@
     <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" s="18" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -638,9 +688,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
@@ -661,7 +711,7 @@
       <c r="R2" s="5"/>
       <c r="S2" s="3"/>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12"/>
       <c r="B3" s="13"/>
       <c r="C3" s="12"/>
@@ -677,12 +727,12 @@
       <c r="M3" s="13"/>
       <c r="N3" s="13"/>
     </row>
-    <row r="4" spans="1:25" ht="36">
+    <row r="4" spans="1:25" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="14" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>15</v>
@@ -697,28 +747,28 @@
         <v>19</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I4" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="14" t="s">
-        <v>26</v>
-      </c>
       <c r="K4" s="14" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="M4" s="14" t="s">
         <v>0</v>
       </c>
       <c r="N4" s="14" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="T4" s="7" t="s">
         <v>5</v>
@@ -727,12 +777,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>10</v>
@@ -747,28 +797,28 @@
         <v>18</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H5" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="K5" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="I5" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="J5" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="K5" s="15" t="s">
-        <v>24</v>
-      </c>
       <c r="L5" s="16" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N5" s="15" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P5" s="9" t="s">
         <v>6</v>
@@ -805,9 +855,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -816,9 +866,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
